--- a/AAII_Financials/Yearly/APD_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/APD_YR_FIN.xlsx
@@ -1008,16 +1008,16 @@
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>26400</v>
+        <v>3679400</v>
       </c>
       <c r="E14" s="3">
         <v>-1516300</v>
       </c>
       <c r="F14" s="3">
-        <v>29000</v>
+        <v>246600</v>
       </c>
       <c r="G14" s="3">
-        <v>6200</v>
+        <v>79900</v>
       </c>
       <c r="H14" s="3">
         <v>-11800</v>
@@ -1128,16 +1128,16 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>12849900</v>
+        <v>9226600</v>
       </c>
       <c r="E17" s="3">
         <v>9253000</v>
       </c>
       <c r="F17" s="3">
-        <v>10164100</v>
+        <v>9946500</v>
       </c>
       <c r="G17" s="3">
-        <v>10310200</v>
+        <v>10236500</v>
       </c>
       <c r="H17" s="3">
         <v>7971400</v>
@@ -1179,16 +1179,16 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-812600</v>
+        <v>2810700</v>
       </c>
       <c r="E18" s="3">
         <v>2847600</v>
       </c>
       <c r="F18" s="3">
-        <v>2435900</v>
+        <v>2653500</v>
       </c>
       <c r="G18" s="3">
-        <v>2388400</v>
+        <v>2462100</v>
       </c>
       <c r="H18" s="3">
         <v>2351600</v>
@@ -1251,7 +1251,7 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-585300</v>
+        <v>-615000</v>
       </c>
       <c r="E20" s="3">
         <v>-695500</v>
@@ -1302,16 +1302,16 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1336900</v>
+        <v>4989900</v>
       </c>
       <c r="E21" s="3">
         <v>4994200</v>
       </c>
       <c r="F21" s="3">
-        <v>4447200</v>
+        <v>4664800</v>
       </c>
       <c r="G21" s="3">
-        <v>4227100</v>
+        <v>4300800</v>
       </c>
       <c r="H21" s="3">
         <v>3958700</v>
@@ -1863,7 +1863,7 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>585300</v>
+        <v>615000</v>
       </c>
       <c r="E32" s="3">
         <v>695500</v>
